--- a/registration_forms/041_dance_class_intake_form--registration_forms.xlsx
+++ b/registration_forms/041_dance_class_intake_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'online_payment',_'label':_'online_payment'}</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'online_payment', 'label': 'Online Payment'}</t>
+          <t>Online Payment</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_person_payment',_'label':_'in_person_payment'}</t>
+          <t>in_person_payment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'in_person_payment', 'label': 'In Person Payment'}</t>
+          <t>In Person Payment</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'parent',_'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'parent', 'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'guardian',_'label':_'guardian'}</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'guardian', 'label': 'Guardian'}</t>
+          <t>Guardian</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'ballet',_'label':_'ballet'}</t>
+          <t>ballet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'ballet', 'label': 'Ballet'}</t>
+          <t>Ballet</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'contemporary',_'label':_'contemporary'}</t>
+          <t>contemporary</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'contemporary', 'label': 'Contemporary'}</t>
+          <t>Contemporary</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'hip_hop',_'label':_'hip_hop'}</t>
+          <t>hip_hop</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'hip_hop', 'label': 'Hip Hop'}</t>
+          <t>Hip Hop</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'tap',_'label':_'tap'}</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'tap', 'label': 'Tap'}</t>
+          <t>Tap</t>
         </is>
       </c>
     </row>
